--- a/docs/Diagramas/Diagrama de Gantt Pronostico.xlsx
+++ b/docs/Diagramas/Diagrama de Gantt Pronostico.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45FA40A-6911-47A9-883A-5E21FE1D626D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CE0518-3EE9-4F2D-8281-C0701AE0AA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
   <si>
     <t>Cree una programación para un proyecto en esta hoja de cálculo.
 Escriba el título de este proyecto en la celda B1. 
@@ -243,9 +243,6 @@
     <t>Tarea 4: Despliegue, Pruebas y Conclusiones</t>
   </si>
   <si>
-    <t>Tarea 5: Bibliografía y Manuales (Anexos)</t>
-  </si>
-  <si>
     <t>Creación del script DDL (Tablas, PK, FK)</t>
   </si>
   <si>
@@ -289,6 +286,12 @@
   </si>
   <si>
     <t>Integración lectura QR con cámara</t>
+  </si>
+  <si>
+    <t>Tarea 5: Bibliografía Manual de instalación y Manual de usuario</t>
+  </si>
+  <si>
+    <t>Tarea 6:Preparacion video y entrega</t>
   </si>
 </sst>
 </file>
@@ -1357,47 +1360,47 @@
     <xf numFmtId="168" fontId="9" fillId="44" borderId="2" xfId="10" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="45" borderId="2" xfId="12" applyFill="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="45" borderId="2" xfId="11" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="45" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="45" borderId="2" xfId="10" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="46" borderId="2" xfId="12" applyFill="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="46" borderId="2" xfId="11" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="46" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="46" borderId="2" xfId="10" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="9">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="8">
       <alignment horizontal="right" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="8" applyBorder="1">
       <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="9">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="45" borderId="2" xfId="12" applyFill="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="45" borderId="2" xfId="11" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="45" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="45" borderId="2" xfId="10" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="46" borderId="2" xfId="12" applyFill="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="46" borderId="2" xfId="11" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="46" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="46" borderId="2" xfId="10" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2007,49 +2010,49 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CG40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:CG41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="42" customWidth="1"/>
-    <col min="2" max="2" width="64.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" hidden="1" customWidth="1"/>
-    <col min="9" max="14" width="3.33203125" customWidth="1"/>
-    <col min="15" max="15" width="9.6640625" customWidth="1"/>
-    <col min="16" max="49" width="3.33203125" customWidth="1"/>
-    <col min="50" max="50" width="7.109375" customWidth="1"/>
-    <col min="51" max="56" width="3.33203125" customWidth="1"/>
+    <col min="1" max="1" width="2.7109375" style="42" customWidth="1"/>
+    <col min="2" max="2" width="64.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="2.7109375" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" hidden="1" customWidth="1"/>
+    <col min="9" max="14" width="3.28515625" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" customWidth="1"/>
+    <col min="16" max="49" width="3.28515625" customWidth="1"/>
+    <col min="50" max="50" width="7.140625" customWidth="1"/>
+    <col min="51" max="56" width="3.28515625" customWidth="1"/>
     <col min="57" max="57" width="7" customWidth="1"/>
-    <col min="58" max="63" width="3.33203125" customWidth="1"/>
-    <col min="64" max="64" width="6.109375" customWidth="1"/>
-    <col min="65" max="65" width="2.77734375" customWidth="1"/>
-    <col min="66" max="66" width="3.5546875" customWidth="1"/>
-    <col min="67" max="67" width="2.44140625" customWidth="1"/>
-    <col min="68" max="68" width="4.33203125" customWidth="1"/>
-    <col min="69" max="69" width="3.5546875" customWidth="1"/>
-    <col min="70" max="70" width="2.88671875" customWidth="1"/>
-    <col min="71" max="71" width="8.109375" customWidth="1"/>
-    <col min="72" max="72" width="2.77734375" customWidth="1"/>
-    <col min="73" max="73" width="3.5546875" customWidth="1"/>
-    <col min="74" max="74" width="2.44140625" customWidth="1"/>
-    <col min="75" max="75" width="4.33203125" customWidth="1"/>
-    <col min="76" max="76" width="3.5546875" customWidth="1"/>
-    <col min="77" max="77" width="2.88671875" customWidth="1"/>
-    <col min="78" max="78" width="8.6640625" customWidth="1"/>
-    <col min="79" max="79" width="2.77734375" customWidth="1"/>
-    <col min="80" max="80" width="3.5546875" customWidth="1"/>
-    <col min="81" max="81" width="2.44140625" customWidth="1"/>
-    <col min="82" max="82" width="4.33203125" customWidth="1"/>
-    <col min="83" max="83" width="3.5546875" customWidth="1"/>
-    <col min="84" max="84" width="2.88671875" customWidth="1"/>
-    <col min="85" max="85" width="5.33203125" customWidth="1"/>
+    <col min="58" max="63" width="3.28515625" customWidth="1"/>
+    <col min="64" max="64" width="6.140625" customWidth="1"/>
+    <col min="65" max="65" width="2.7109375" customWidth="1"/>
+    <col min="66" max="66" width="3.5703125" customWidth="1"/>
+    <col min="67" max="67" width="2.42578125" customWidth="1"/>
+    <col min="68" max="68" width="4.28515625" customWidth="1"/>
+    <col min="69" max="69" width="3.5703125" customWidth="1"/>
+    <col min="70" max="70" width="2.85546875" customWidth="1"/>
+    <col min="71" max="71" width="8.140625" customWidth="1"/>
+    <col min="72" max="72" width="2.7109375" customWidth="1"/>
+    <col min="73" max="73" width="3.5703125" customWidth="1"/>
+    <col min="74" max="74" width="2.42578125" customWidth="1"/>
+    <col min="75" max="75" width="4.28515625" customWidth="1"/>
+    <col min="76" max="76" width="3.5703125" customWidth="1"/>
+    <col min="77" max="77" width="2.85546875" customWidth="1"/>
+    <col min="78" max="78" width="8.7109375" customWidth="1"/>
+    <col min="79" max="79" width="2.7109375" customWidth="1"/>
+    <col min="80" max="80" width="3.5703125" customWidth="1"/>
+    <col min="81" max="81" width="2.42578125" customWidth="1"/>
+    <col min="82" max="82" width="4.28515625" customWidth="1"/>
+    <col min="83" max="83" width="3.5703125" customWidth="1"/>
+    <col min="84" max="84" width="2.85546875" customWidth="1"/>
+    <col min="85" max="85" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -2065,7 +2068,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
@@ -2076,145 +2079,145 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="42" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="88" t="s">
+      <c r="C3" s="100" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="89"/>
-      <c r="E3" s="93">
+      <c r="D3" s="101"/>
+      <c r="E3" s="99">
         <v>46293</v>
       </c>
-      <c r="F3" s="93"/>
+      <c r="F3" s="99"/>
     </row>
-    <row r="4" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="88" t="s">
+      <c r="C4" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="89"/>
+      <c r="D4" s="101"/>
       <c r="E4" s="7">
         <v>1</v>
       </c>
-      <c r="I4" s="90">
+      <c r="I4" s="96">
         <f>I5</f>
         <v>46293</v>
       </c>
-      <c r="J4" s="91"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="91"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="92"/>
-      <c r="P4" s="90">
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="97"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="96">
         <f>P5</f>
         <v>46300</v>
       </c>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="91"/>
-      <c r="S4" s="91"/>
-      <c r="T4" s="91"/>
-      <c r="U4" s="91"/>
-      <c r="V4" s="92"/>
-      <c r="W4" s="90">
+      <c r="Q4" s="97"/>
+      <c r="R4" s="97"/>
+      <c r="S4" s="97"/>
+      <c r="T4" s="97"/>
+      <c r="U4" s="97"/>
+      <c r="V4" s="98"/>
+      <c r="W4" s="96">
         <f>W5</f>
         <v>46307</v>
       </c>
-      <c r="X4" s="91"/>
-      <c r="Y4" s="91"/>
-      <c r="Z4" s="91"/>
-      <c r="AA4" s="91"/>
-      <c r="AB4" s="91"/>
-      <c r="AC4" s="92"/>
-      <c r="AD4" s="90">
+      <c r="X4" s="97"/>
+      <c r="Y4" s="97"/>
+      <c r="Z4" s="97"/>
+      <c r="AA4" s="97"/>
+      <c r="AB4" s="97"/>
+      <c r="AC4" s="98"/>
+      <c r="AD4" s="96">
         <f>AD5</f>
         <v>46314</v>
       </c>
-      <c r="AE4" s="91"/>
-      <c r="AF4" s="91"/>
-      <c r="AG4" s="91"/>
-      <c r="AH4" s="91"/>
-      <c r="AI4" s="91"/>
-      <c r="AJ4" s="92"/>
-      <c r="AK4" s="90">
+      <c r="AE4" s="97"/>
+      <c r="AF4" s="97"/>
+      <c r="AG4" s="97"/>
+      <c r="AH4" s="97"/>
+      <c r="AI4" s="97"/>
+      <c r="AJ4" s="98"/>
+      <c r="AK4" s="96">
         <f>AK5</f>
         <v>46321</v>
       </c>
-      <c r="AL4" s="91"/>
-      <c r="AM4" s="91"/>
-      <c r="AN4" s="91"/>
-      <c r="AO4" s="91"/>
-      <c r="AP4" s="91"/>
-      <c r="AQ4" s="92"/>
-      <c r="AR4" s="90">
+      <c r="AL4" s="97"/>
+      <c r="AM4" s="97"/>
+      <c r="AN4" s="97"/>
+      <c r="AO4" s="97"/>
+      <c r="AP4" s="97"/>
+      <c r="AQ4" s="98"/>
+      <c r="AR4" s="96">
         <f>AR5</f>
         <v>46328</v>
       </c>
-      <c r="AS4" s="91"/>
-      <c r="AT4" s="91"/>
-      <c r="AU4" s="91"/>
-      <c r="AV4" s="91"/>
-      <c r="AW4" s="91"/>
-      <c r="AX4" s="92"/>
-      <c r="AY4" s="90">
+      <c r="AS4" s="97"/>
+      <c r="AT4" s="97"/>
+      <c r="AU4" s="97"/>
+      <c r="AV4" s="97"/>
+      <c r="AW4" s="97"/>
+      <c r="AX4" s="98"/>
+      <c r="AY4" s="96">
         <f>AY5</f>
         <v>46335</v>
       </c>
-      <c r="AZ4" s="91"/>
-      <c r="BA4" s="91"/>
-      <c r="BB4" s="91"/>
-      <c r="BC4" s="91"/>
-      <c r="BD4" s="91"/>
-      <c r="BE4" s="92"/>
-      <c r="BF4" s="90">
+      <c r="AZ4" s="97"/>
+      <c r="BA4" s="97"/>
+      <c r="BB4" s="97"/>
+      <c r="BC4" s="97"/>
+      <c r="BD4" s="97"/>
+      <c r="BE4" s="98"/>
+      <c r="BF4" s="96">
         <f>BF5</f>
         <v>46342</v>
       </c>
-      <c r="BG4" s="91"/>
-      <c r="BH4" s="91"/>
-      <c r="BI4" s="91"/>
-      <c r="BJ4" s="91"/>
-      <c r="BK4" s="91"/>
-      <c r="BL4" s="92"/>
-      <c r="BM4" s="90">
+      <c r="BG4" s="97"/>
+      <c r="BH4" s="97"/>
+      <c r="BI4" s="97"/>
+      <c r="BJ4" s="97"/>
+      <c r="BK4" s="97"/>
+      <c r="BL4" s="98"/>
+      <c r="BM4" s="96">
         <f>BM5</f>
         <v>46349</v>
       </c>
-      <c r="BN4" s="91"/>
-      <c r="BO4" s="91"/>
-      <c r="BP4" s="91"/>
-      <c r="BQ4" s="91"/>
-      <c r="BR4" s="91"/>
-      <c r="BS4" s="92"/>
-      <c r="BT4" s="90">
+      <c r="BN4" s="97"/>
+      <c r="BO4" s="97"/>
+      <c r="BP4" s="97"/>
+      <c r="BQ4" s="97"/>
+      <c r="BR4" s="97"/>
+      <c r="BS4" s="98"/>
+      <c r="BT4" s="96">
         <f>BT5</f>
         <v>46356</v>
       </c>
-      <c r="BU4" s="91"/>
-      <c r="BV4" s="91"/>
-      <c r="BW4" s="91"/>
-      <c r="BX4" s="91"/>
-      <c r="BY4" s="91"/>
-      <c r="BZ4" s="92"/>
-      <c r="CA4" s="90">
+      <c r="BU4" s="97"/>
+      <c r="BV4" s="97"/>
+      <c r="BW4" s="97"/>
+      <c r="BX4" s="97"/>
+      <c r="BY4" s="97"/>
+      <c r="BZ4" s="98"/>
+      <c r="CA4" s="96">
         <f>CA5</f>
         <v>46363</v>
       </c>
-      <c r="CB4" s="91"/>
-      <c r="CC4" s="91"/>
-      <c r="CD4" s="91"/>
-      <c r="CE4" s="91"/>
-      <c r="CF4" s="91"/>
-      <c r="CG4" s="92"/>
+      <c r="CB4" s="97"/>
+      <c r="CC4" s="97"/>
+      <c r="CD4" s="97"/>
+      <c r="CE4" s="97"/>
+      <c r="CF4" s="97"/>
+      <c r="CG4" s="98"/>
     </row>
-    <row r="5" spans="1:85" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="43" t="s">
         <v>4</v>
       </c>
@@ -2533,7 +2536,7 @@
         <v>46369</v>
       </c>
     </row>
-    <row r="6" spans="1:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="43" t="s">
         <v>5</v>
       </c>
@@ -2865,7 +2868,7 @@
         <v>d</v>
       </c>
     </row>
-    <row r="7" spans="1:85" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:85" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="42" t="s">
         <v>6</v>
       </c>
@@ -2953,7 +2956,7 @@
       <c r="CF7" s="28"/>
       <c r="CG7" s="28"/>
     </row>
-    <row r="8" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="43" t="s">
         <v>7</v>
       </c>
@@ -2970,7 +2973,7 @@
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="14">
-        <f t="shared" ref="H8:H37" si="23">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+        <f t="shared" ref="H8:H38" si="23">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v>72</v>
       </c>
       <c r="I8" s="28"/>
@@ -3051,7 +3054,7 @@
       <c r="CF8" s="28"/>
       <c r="CG8" s="28"/>
     </row>
-    <row r="9" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="43" t="s">
         <v>8</v>
       </c>
@@ -3153,7 +3156,7 @@
       <c r="CF9" s="28"/>
       <c r="CG9" s="28"/>
     </row>
-    <row r="10" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="43" t="s">
         <v>9</v>
       </c>
@@ -3255,7 +3258,7 @@
       <c r="CF10" s="28"/>
       <c r="CG10" s="28"/>
     </row>
-    <row r="11" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="42"/>
       <c r="B11" s="56" t="s">
         <v>44</v>
@@ -3352,7 +3355,7 @@
       <c r="CF11" s="28"/>
       <c r="CG11" s="28"/>
     </row>
-    <row r="12" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="42"/>
       <c r="B12" s="56" t="s">
         <v>45</v>
@@ -3449,7 +3452,7 @@
       <c r="CF12" s="28"/>
       <c r="CG12" s="28"/>
     </row>
-    <row r="13" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="42"/>
       <c r="B13" s="56" t="s">
         <v>46</v>
@@ -3546,7 +3549,7 @@
       <c r="CF13" s="28"/>
       <c r="CG13" s="28"/>
     </row>
-    <row r="14" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="42"/>
       <c r="B14" s="56" t="s">
         <v>47</v>
@@ -3643,7 +3646,7 @@
       <c r="CF14" s="28"/>
       <c r="CG14" s="28"/>
     </row>
-    <row r="15" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="42"/>
       <c r="B15" s="56" t="s">
         <v>53</v>
@@ -3658,12 +3661,12 @@
         <v>46358</v>
       </c>
       <c r="F15" s="75">
-        <v>46361</v>
+        <v>46359</v>
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="14">
         <f t="shared" si="23"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I15" s="28"/>
       <c r="J15" s="28"/>
@@ -3743,10 +3746,10 @@
       <c r="CF15" s="28"/>
       <c r="CG15" s="28"/>
     </row>
-    <row r="16" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="42"/>
       <c r="B16" s="56" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="C16" s="50" t="s">
         <v>43</v>
@@ -3761,10 +3764,7 @@
         <v>46364</v>
       </c>
       <c r="G16" s="14"/>
-      <c r="H16" s="14">
-        <f t="shared" si="23"/>
-        <v>3</v>
-      </c>
+      <c r="H16" s="14"/>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="28"/>
@@ -3781,7 +3781,7 @@
       <c r="V16" s="28"/>
       <c r="W16" s="28"/>
       <c r="X16" s="28"/>
-      <c r="Y16" s="28"/>
+      <c r="Y16" s="29"/>
       <c r="Z16" s="28"/>
       <c r="AA16" s="28"/>
       <c r="AB16" s="28"/>
@@ -3843,25 +3843,27 @@
       <c r="CF16" s="28"/>
       <c r="CG16" s="28"/>
     </row>
-    <row r="17" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="66">
-        <v>46317</v>
-      </c>
-      <c r="F17" s="67">
-        <v>46326</v>
+    <row r="17" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="42"/>
+      <c r="B17" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="50" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="17">
+        <v>0</v>
+      </c>
+      <c r="E17" s="75">
+        <v>46364</v>
+      </c>
+      <c r="F17" s="75">
+        <v>46367</v>
       </c>
       <c r="G17" s="14"/>
       <c r="H17" s="14">
         <f t="shared" si="23"/>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I17" s="28"/>
       <c r="J17" s="28"/>
@@ -3941,27 +3943,25 @@
       <c r="CF17" s="28"/>
       <c r="CG17" s="28"/>
     </row>
-    <row r="18" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="43"/>
-      <c r="B18" s="57" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="52" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="20">
-        <v>0</v>
-      </c>
-      <c r="E18" s="76">
+    <row r="18" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="51"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="66">
         <v>46317</v>
       </c>
-      <c r="F18" s="76">
-        <v>46319</v>
+      <c r="F18" s="67">
+        <v>46326</v>
       </c>
       <c r="G18" s="14"/>
       <c r="H18" s="14">
         <f t="shared" si="23"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I18" s="28"/>
       <c r="J18" s="28"/>
@@ -4041,10 +4041,10 @@
       <c r="CF18" s="28"/>
       <c r="CG18" s="28"/>
     </row>
-    <row r="19" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="42"/>
+    <row r="19" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="43"/>
       <c r="B19" s="57" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C19" s="52" t="s">
         <v>43</v>
@@ -4053,10 +4053,10 @@
         <v>0</v>
       </c>
       <c r="E19" s="76">
-        <v>46320</v>
+        <v>46317</v>
       </c>
       <c r="F19" s="76">
-        <v>46322</v>
+        <v>46319</v>
       </c>
       <c r="G19" s="14"/>
       <c r="H19" s="14">
@@ -4075,8 +4075,8 @@
       <c r="R19" s="28"/>
       <c r="S19" s="28"/>
       <c r="T19" s="28"/>
-      <c r="U19" s="29"/>
-      <c r="V19" s="29"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="28"/>
       <c r="W19" s="28"/>
       <c r="X19" s="28"/>
       <c r="Y19" s="28"/>
@@ -4141,10 +4141,10 @@
       <c r="CF19" s="28"/>
       <c r="CG19" s="28"/>
     </row>
-    <row r="20" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="42"/>
       <c r="B20" s="57" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C20" s="52" t="s">
         <v>43</v>
@@ -4153,15 +4153,15 @@
         <v>0</v>
       </c>
       <c r="E20" s="76">
-        <v>46323</v>
+        <v>46320</v>
       </c>
       <c r="F20" s="76">
-        <v>46323</v>
+        <v>46322</v>
       </c>
       <c r="G20" s="14"/>
       <c r="H20" s="14">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" s="28"/>
       <c r="J20" s="28"/>
@@ -4175,8 +4175,8 @@
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
       <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="28"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
       <c r="W20" s="28"/>
       <c r="X20" s="28"/>
       <c r="Y20" s="28"/>
@@ -4241,10 +4241,10 @@
       <c r="CF20" s="28"/>
       <c r="CG20" s="28"/>
     </row>
-    <row r="21" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="42"/>
       <c r="B21" s="57" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C21" s="52" t="s">
         <v>43</v>
@@ -4253,15 +4253,15 @@
         <v>0</v>
       </c>
       <c r="E21" s="76">
-        <v>46324</v>
+        <v>46323</v>
       </c>
       <c r="F21" s="76">
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="G21" s="14"/>
       <c r="H21" s="14">
         <f t="shared" si="23"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="28"/>
       <c r="J21" s="28"/>
@@ -4279,7 +4279,7 @@
       <c r="V21" s="28"/>
       <c r="W21" s="28"/>
       <c r="X21" s="28"/>
-      <c r="Y21" s="29"/>
+      <c r="Y21" s="28"/>
       <c r="Z21" s="28"/>
       <c r="AA21" s="28"/>
       <c r="AB21" s="28"/>
@@ -4341,10 +4341,10 @@
       <c r="CF21" s="28"/>
       <c r="CG21" s="28"/>
     </row>
-    <row r="22" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="42"/>
       <c r="B22" s="57" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C22" s="52" t="s">
         <v>43</v>
@@ -4353,15 +4353,15 @@
         <v>0</v>
       </c>
       <c r="E22" s="76">
-        <v>46326</v>
+        <v>46324</v>
       </c>
       <c r="F22" s="76">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="G22" s="14"/>
       <c r="H22" s="14">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" s="28"/>
       <c r="J22" s="28"/>
@@ -4379,7 +4379,7 @@
       <c r="V22" s="28"/>
       <c r="W22" s="28"/>
       <c r="X22" s="28"/>
-      <c r="Y22" s="28"/>
+      <c r="Y22" s="29"/>
       <c r="Z22" s="28"/>
       <c r="AA22" s="28"/>
       <c r="AB22" s="28"/>
@@ -4441,25 +4441,27 @@
       <c r="CF22" s="28"/>
       <c r="CG22" s="28"/>
     </row>
-    <row r="23" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="53"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="68">
-        <v>46327</v>
-      </c>
-      <c r="F23" s="69">
-        <v>46340</v>
+    <row r="23" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="42"/>
+      <c r="B23" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="20">
+        <v>0</v>
+      </c>
+      <c r="E23" s="76">
+        <v>46326</v>
+      </c>
+      <c r="F23" s="76">
+        <v>46326</v>
       </c>
       <c r="G23" s="14"/>
       <c r="H23" s="14">
         <f t="shared" si="23"/>
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I23" s="28"/>
       <c r="J23" s="28"/>
@@ -4539,27 +4541,25 @@
       <c r="CF23" s="28"/>
       <c r="CG23" s="28"/>
     </row>
-    <row r="24" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="42"/>
-      <c r="B24" s="58" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="54" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="23">
-        <v>0</v>
-      </c>
-      <c r="E24" s="77">
+    <row r="24" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="53"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="68">
         <v>46327</v>
       </c>
-      <c r="F24" s="77">
-        <v>46329</v>
+      <c r="F24" s="69">
+        <v>46340</v>
       </c>
       <c r="G24" s="14"/>
       <c r="H24" s="14">
         <f t="shared" si="23"/>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I24" s="28"/>
       <c r="J24" s="28"/>
@@ -4639,10 +4639,10 @@
       <c r="CF24" s="28"/>
       <c r="CG24" s="28"/>
     </row>
-    <row r="25" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="42"/>
       <c r="B25" s="58" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C25" s="54" t="s">
         <v>43</v>
@@ -4651,10 +4651,10 @@
         <v>0</v>
       </c>
       <c r="E25" s="77">
-        <v>46330</v>
+        <v>46327</v>
       </c>
       <c r="F25" s="77">
-        <v>46332</v>
+        <v>46329</v>
       </c>
       <c r="G25" s="14"/>
       <c r="H25" s="14">
@@ -4739,10 +4739,10 @@
       <c r="CF25" s="28"/>
       <c r="CG25" s="28"/>
     </row>
-    <row r="26" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="42"/>
       <c r="B26" s="58" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C26" s="54" t="s">
         <v>43</v>
@@ -4751,15 +4751,15 @@
         <v>0</v>
       </c>
       <c r="E26" s="77">
-        <v>46333</v>
+        <v>46330</v>
       </c>
       <c r="F26" s="77">
-        <v>46336</v>
+        <v>46332</v>
       </c>
       <c r="G26" s="14"/>
       <c r="H26" s="14">
         <f t="shared" si="23"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I26" s="28"/>
       <c r="J26" s="28"/>
@@ -4839,10 +4839,10 @@
       <c r="CF26" s="28"/>
       <c r="CG26" s="28"/>
     </row>
-    <row r="27" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="42"/>
       <c r="B27" s="58" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C27" s="54" t="s">
         <v>43</v>
@@ -4851,10 +4851,10 @@
         <v>0</v>
       </c>
       <c r="E27" s="77">
-        <v>46337</v>
+        <v>46333</v>
       </c>
       <c r="F27" s="77">
-        <v>46340</v>
+        <v>46336</v>
       </c>
       <c r="G27" s="14"/>
       <c r="H27" s="14">
@@ -4939,25 +4939,27 @@
       <c r="CF27" s="28"/>
       <c r="CG27" s="28"/>
     </row>
-    <row r="28" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="81" t="s">
-        <v>62</v>
-      </c>
-      <c r="C28" s="79"/>
-      <c r="D28" s="80"/>
-      <c r="E28" s="82">
-        <v>46341</v>
-      </c>
-      <c r="F28" s="83">
-        <v>46349</v>
+    <row r="28" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="42"/>
+      <c r="B28" s="58" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="23">
+        <v>0</v>
+      </c>
+      <c r="E28" s="77">
+        <v>46337</v>
+      </c>
+      <c r="F28" s="77">
+        <v>46340</v>
       </c>
       <c r="G28" s="14"/>
       <c r="H28" s="14">
         <f t="shared" si="23"/>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I28" s="28"/>
       <c r="J28" s="28"/>
@@ -5037,29 +5039,25 @@
       <c r="CF28" s="28"/>
       <c r="CG28" s="28"/>
     </row>
-    <row r="29" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="84" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="85" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="86">
-        <v>0</v>
-      </c>
-      <c r="E29" s="87">
+    <row r="29" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="79"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="82">
         <v>46341</v>
       </c>
-      <c r="F29" s="87">
-        <v>46344</v>
+      <c r="F29" s="83">
+        <v>46349</v>
       </c>
       <c r="G29" s="14"/>
       <c r="H29" s="14">
         <f t="shared" si="23"/>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I29" s="28"/>
       <c r="J29" s="28"/>
@@ -5139,9 +5137,12 @@
       <c r="CF29" s="28"/>
       <c r="CG29" s="28"/>
     </row>
-    <row r="30" spans="1:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="43" t="s">
+        <v>13</v>
+      </c>
       <c r="B30" s="84" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C30" s="85" t="s">
         <v>43</v>
@@ -5150,15 +5151,15 @@
         <v>0</v>
       </c>
       <c r="E30" s="87">
-        <v>46345</v>
+        <v>46341</v>
       </c>
       <c r="F30" s="87">
-        <v>46346</v>
+        <v>46344</v>
       </c>
       <c r="G30" s="14"/>
       <c r="H30" s="14">
         <f t="shared" si="23"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I30" s="28"/>
       <c r="J30" s="28"/>
@@ -5238,9 +5239,9 @@
       <c r="CF30" s="28"/>
       <c r="CG30" s="28"/>
     </row>
-    <row r="31" spans="1:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="84" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C31" s="85" t="s">
         <v>43</v>
@@ -5249,15 +5250,15 @@
         <v>0</v>
       </c>
       <c r="E31" s="87">
-        <v>46347</v>
+        <v>46345</v>
       </c>
       <c r="F31" s="87">
-        <v>46349</v>
+        <v>46346</v>
       </c>
       <c r="G31" s="14"/>
       <c r="H31" s="14">
         <f t="shared" si="23"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I31" s="28"/>
       <c r="J31" s="28"/>
@@ -5337,20 +5338,27 @@
       <c r="CF31" s="28"/>
       <c r="CG31" s="28"/>
     </row>
-    <row r="32" spans="1:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="98" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" s="99"/>
-      <c r="D32" s="100"/>
-      <c r="E32" s="101">
-        <v>46350</v>
-      </c>
-      <c r="F32" s="101">
-        <v>46357</v>
+    <row r="32" spans="1:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="84" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="85" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="86">
+        <v>0</v>
+      </c>
+      <c r="E32" s="87">
+        <v>46347</v>
+      </c>
+      <c r="F32" s="87">
+        <v>46349</v>
       </c>
       <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
+      <c r="H32" s="14">
+        <f t="shared" si="23"/>
+        <v>3</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
@@ -5429,21 +5437,17 @@
       <c r="CF32" s="28"/>
       <c r="CG32" s="28"/>
     </row>
-    <row r="33" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="94" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="95" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" s="96">
-        <v>0</v>
-      </c>
-      <c r="E33" s="97">
+    <row r="33" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="92" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="93"/>
+      <c r="D33" s="94"/>
+      <c r="E33" s="95">
         <v>46350</v>
       </c>
-      <c r="F33" s="97">
-        <v>46352</v>
+      <c r="F33" s="95">
+        <v>46357</v>
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
@@ -5525,21 +5529,21 @@
       <c r="CF33" s="28"/>
       <c r="CG33" s="28"/>
     </row>
-    <row r="34" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="94" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="95" t="s">
+    <row r="34" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="88" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="96">
+      <c r="D34" s="90">
         <v>0</v>
       </c>
-      <c r="E34" s="97">
-        <v>46353</v>
-      </c>
-      <c r="F34" s="97">
-        <v>46355</v>
+      <c r="E34" s="91">
+        <v>46350</v>
+      </c>
+      <c r="F34" s="91">
+        <v>46352</v>
       </c>
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
@@ -5621,27 +5625,24 @@
       <c r="CF34" s="28"/>
       <c r="CG34" s="28"/>
     </row>
-    <row r="35" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="94" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" s="95" t="s">
+    <row r="35" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="88" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="89" t="s">
         <v>43</v>
       </c>
-      <c r="D35" s="96">
+      <c r="D35" s="90">
         <v>0</v>
       </c>
-      <c r="E35" s="97">
-        <v>46356</v>
-      </c>
-      <c r="F35" s="97">
-        <v>46357</v>
+      <c r="E35" s="91">
+        <v>46353</v>
+      </c>
+      <c r="F35" s="91">
+        <v>46355</v>
       </c>
       <c r="G35" s="14"/>
-      <c r="H35" s="14">
-        <f t="shared" si="23"/>
-        <v>2</v>
-      </c>
+      <c r="H35" s="14"/>
       <c r="I35" s="28"/>
       <c r="J35" s="28"/>
       <c r="K35" s="28"/>
@@ -5720,16 +5721,26 @@
       <c r="CF35" s="28"/>
       <c r="CG35" s="28"/>
     </row>
-    <row r="36" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="59"/>
-      <c r="C36" s="55"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="78"/>
-      <c r="F36" s="78"/>
+    <row r="36" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="88" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="89" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="90">
+        <v>0</v>
+      </c>
+      <c r="E36" s="91">
+        <v>46356</v>
+      </c>
+      <c r="F36" s="91">
+        <v>46357</v>
+      </c>
       <c r="G36" s="14"/>
-      <c r="H36" s="14" t="str">
+      <c r="H36" s="14">
         <f t="shared" si="23"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="I36" s="28"/>
       <c r="J36" s="28"/>
@@ -5809,109 +5820,203 @@
       <c r="CF36" s="28"/>
       <c r="CG36" s="28"/>
     </row>
-    <row r="37" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37" s="25"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27" t="str">
+    <row r="37" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="59"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="78"/>
+      <c r="F37" s="78"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
-      <c r="S37" s="30"/>
-      <c r="T37" s="30"/>
-      <c r="U37" s="30"/>
-      <c r="V37" s="30"/>
-      <c r="W37" s="30"/>
-      <c r="X37" s="30"/>
-      <c r="Y37" s="30"/>
-      <c r="Z37" s="30"/>
-      <c r="AA37" s="30"/>
-      <c r="AB37" s="30"/>
-      <c r="AC37" s="30"/>
-      <c r="AD37" s="30"/>
-      <c r="AE37" s="30"/>
-      <c r="AF37" s="30"/>
-      <c r="AG37" s="30"/>
-      <c r="AH37" s="30"/>
-      <c r="AI37" s="30"/>
-      <c r="AJ37" s="30"/>
-      <c r="AK37" s="30"/>
-      <c r="AL37" s="30"/>
-      <c r="AM37" s="30"/>
-      <c r="AN37" s="30"/>
-      <c r="AO37" s="30"/>
-      <c r="AP37" s="30"/>
-      <c r="AQ37" s="30"/>
-      <c r="AR37" s="30"/>
-      <c r="AS37" s="30"/>
-      <c r="AT37" s="30"/>
-      <c r="AU37" s="30"/>
-      <c r="AV37" s="30"/>
-      <c r="AW37" s="30"/>
-      <c r="AX37" s="30"/>
-      <c r="AY37" s="30"/>
-      <c r="AZ37" s="30"/>
-      <c r="BA37" s="30"/>
-      <c r="BB37" s="30"/>
-      <c r="BC37" s="30"/>
-      <c r="BD37" s="30"/>
-      <c r="BE37" s="30"/>
-      <c r="BF37" s="30"/>
-      <c r="BG37" s="30"/>
-      <c r="BH37" s="30"/>
-      <c r="BI37" s="30"/>
-      <c r="BJ37" s="30"/>
-      <c r="BK37" s="30"/>
-      <c r="BL37" s="30"/>
-      <c r="BM37" s="30"/>
-      <c r="BN37" s="30"/>
-      <c r="BO37" s="30"/>
-      <c r="BP37" s="30"/>
-      <c r="BQ37" s="30"/>
-      <c r="BR37" s="30"/>
-      <c r="BS37" s="30"/>
-      <c r="BT37" s="30"/>
-      <c r="BU37" s="30"/>
-      <c r="BV37" s="30"/>
-      <c r="BW37" s="30"/>
-      <c r="BX37" s="30"/>
-      <c r="BY37" s="30"/>
-      <c r="BZ37" s="30"/>
-      <c r="CA37" s="30"/>
-      <c r="CB37" s="30"/>
-      <c r="CC37" s="30"/>
-      <c r="CD37" s="30"/>
-      <c r="CE37" s="30"/>
-      <c r="CF37" s="30"/>
-      <c r="CG37" s="30"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="28"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="28"/>
+      <c r="Y37" s="28"/>
+      <c r="Z37" s="28"/>
+      <c r="AA37" s="28"/>
+      <c r="AB37" s="28"/>
+      <c r="AC37" s="28"/>
+      <c r="AD37" s="28"/>
+      <c r="AE37" s="28"/>
+      <c r="AF37" s="28"/>
+      <c r="AG37" s="28"/>
+      <c r="AH37" s="28"/>
+      <c r="AI37" s="28"/>
+      <c r="AJ37" s="28"/>
+      <c r="AK37" s="28"/>
+      <c r="AL37" s="28"/>
+      <c r="AM37" s="28"/>
+      <c r="AN37" s="28"/>
+      <c r="AO37" s="28"/>
+      <c r="AP37" s="28"/>
+      <c r="AQ37" s="28"/>
+      <c r="AR37" s="28"/>
+      <c r="AS37" s="28"/>
+      <c r="AT37" s="28"/>
+      <c r="AU37" s="28"/>
+      <c r="AV37" s="28"/>
+      <c r="AW37" s="28"/>
+      <c r="AX37" s="28"/>
+      <c r="AY37" s="28"/>
+      <c r="AZ37" s="28"/>
+      <c r="BA37" s="28"/>
+      <c r="BB37" s="28"/>
+      <c r="BC37" s="28"/>
+      <c r="BD37" s="28"/>
+      <c r="BE37" s="28"/>
+      <c r="BF37" s="28"/>
+      <c r="BG37" s="28"/>
+      <c r="BH37" s="28"/>
+      <c r="BI37" s="28"/>
+      <c r="BJ37" s="28"/>
+      <c r="BK37" s="28"/>
+      <c r="BL37" s="28"/>
+      <c r="BM37" s="28"/>
+      <c r="BN37" s="28"/>
+      <c r="BO37" s="28"/>
+      <c r="BP37" s="28"/>
+      <c r="BQ37" s="28"/>
+      <c r="BR37" s="28"/>
+      <c r="BS37" s="28"/>
+      <c r="BT37" s="28"/>
+      <c r="BU37" s="28"/>
+      <c r="BV37" s="28"/>
+      <c r="BW37" s="28"/>
+      <c r="BX37" s="28"/>
+      <c r="BY37" s="28"/>
+      <c r="BZ37" s="28"/>
+      <c r="CA37" s="28"/>
+      <c r="CB37" s="28"/>
+      <c r="CC37" s="28"/>
+      <c r="CD37" s="28"/>
+      <c r="CE37" s="28"/>
+      <c r="CF37" s="28"/>
+      <c r="CG37" s="28"/>
     </row>
-    <row r="38" spans="2:85" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G38" s="6"/>
+    <row r="38" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="25"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="27" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="30"/>
+      <c r="N38" s="30"/>
+      <c r="O38" s="30"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="30"/>
+      <c r="R38" s="30"/>
+      <c r="S38" s="30"/>
+      <c r="T38" s="30"/>
+      <c r="U38" s="30"/>
+      <c r="V38" s="30"/>
+      <c r="W38" s="30"/>
+      <c r="X38" s="30"/>
+      <c r="Y38" s="30"/>
+      <c r="Z38" s="30"/>
+      <c r="AA38" s="30"/>
+      <c r="AB38" s="30"/>
+      <c r="AC38" s="30"/>
+      <c r="AD38" s="30"/>
+      <c r="AE38" s="30"/>
+      <c r="AF38" s="30"/>
+      <c r="AG38" s="30"/>
+      <c r="AH38" s="30"/>
+      <c r="AI38" s="30"/>
+      <c r="AJ38" s="30"/>
+      <c r="AK38" s="30"/>
+      <c r="AL38" s="30"/>
+      <c r="AM38" s="30"/>
+      <c r="AN38" s="30"/>
+      <c r="AO38" s="30"/>
+      <c r="AP38" s="30"/>
+      <c r="AQ38" s="30"/>
+      <c r="AR38" s="30"/>
+      <c r="AS38" s="30"/>
+      <c r="AT38" s="30"/>
+      <c r="AU38" s="30"/>
+      <c r="AV38" s="30"/>
+      <c r="AW38" s="30"/>
+      <c r="AX38" s="30"/>
+      <c r="AY38" s="30"/>
+      <c r="AZ38" s="30"/>
+      <c r="BA38" s="30"/>
+      <c r="BB38" s="30"/>
+      <c r="BC38" s="30"/>
+      <c r="BD38" s="30"/>
+      <c r="BE38" s="30"/>
+      <c r="BF38" s="30"/>
+      <c r="BG38" s="30"/>
+      <c r="BH38" s="30"/>
+      <c r="BI38" s="30"/>
+      <c r="BJ38" s="30"/>
+      <c r="BK38" s="30"/>
+      <c r="BL38" s="30"/>
+      <c r="BM38" s="30"/>
+      <c r="BN38" s="30"/>
+      <c r="BO38" s="30"/>
+      <c r="BP38" s="30"/>
+      <c r="BQ38" s="30"/>
+      <c r="BR38" s="30"/>
+      <c r="BS38" s="30"/>
+      <c r="BT38" s="30"/>
+      <c r="BU38" s="30"/>
+      <c r="BV38" s="30"/>
+      <c r="BW38" s="30"/>
+      <c r="BX38" s="30"/>
+      <c r="BY38" s="30"/>
+      <c r="BZ38" s="30"/>
+      <c r="CA38" s="30"/>
+      <c r="CB38" s="30"/>
+      <c r="CC38" s="30"/>
+      <c r="CD38" s="30"/>
+      <c r="CE38" s="30"/>
+      <c r="CF38" s="30"/>
+      <c r="CG38" s="30"/>
     </row>
-    <row r="39" spans="2:85" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="11"/>
-      <c r="F39" s="44"/>
+    <row r="39" spans="2:85" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G39" s="6"/>
     </row>
-    <row r="40" spans="2:85" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="12"/>
+    <row r="40" spans="2:85" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="11"/>
+      <c r="F40" s="44"/>
+    </row>
+    <row r="41" spans="2:85" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BM4:BS4"/>
     <mergeCell ref="BT4:BZ4"/>
     <mergeCell ref="CA4:CG4"/>
@@ -5921,13 +6026,8 @@
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
-  <conditionalFormatting sqref="D7:D37">
+  <conditionalFormatting sqref="D7:D38">
     <cfRule type="dataBar" priority="23">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -5941,12 +6041,12 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:CG37">
+  <conditionalFormatting sqref="I5:CG38">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>AND(TODAY()&gt;=I$5,TODAY()&lt;J$5)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I7:CG37">
+  <conditionalFormatting sqref="I7:CG38">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND(task_start&lt;=I$5,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$5)</formula>
     </cfRule>
@@ -5985,7 +6085,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D7:D37</xm:sqref>
+          <xm:sqref>D7:D38</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -5996,86 +6096,86 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="87.109375" style="32" customWidth="1"/>
-    <col min="2" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="87.140625" style="32" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="46.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:2" s="34" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:2" s="34" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="33"/>
     </row>
-    <row r="3" spans="1:2" s="38" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" s="38" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="63" t="s">
         <v>27</v>
       </c>
       <c r="B3" s="39"/>
     </row>
-    <row r="4" spans="1:2" s="35" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:2" s="35" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A4" s="36" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="37" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="36" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="32" customFormat="1" ht="215.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" s="32" customFormat="1" ht="215.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="35" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:2" s="35" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A8" s="36" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="75" x14ac:dyDescent="0.2">
       <c r="A9" s="37" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="32" customFormat="1" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" s="32" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="35" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:2" s="35" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A11" s="36" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" s="37" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="32" customFormat="1" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" s="32" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="40" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="35" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:2" s="35" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A14" s="36" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="96.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="96.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="37" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="90" x14ac:dyDescent="0.2">
       <c r="A16" s="37" t="s">
         <v>40</v>
       </c>
@@ -6094,6 +6194,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6381,36 +6510,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6429,24 +6549,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/docs/Diagramas/Diagrama de Gantt Pronostico.xlsx
+++ b/docs/Diagramas/Diagrama de Gantt Pronostico.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CE0518-3EE9-4F2D-8281-C0701AE0AA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33371900-6168-4392-B3D4-C209B398ACFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ProjectSchedule" sheetId="11" r:id="rId1"/>
@@ -204,33 +204,9 @@
     <t>Las empresas encontrarán plantillas de facturas, partes de horas, informes financieros, planificación de proyectos y plantillas para hacer un seguimiento del inventario. Los profesores y los estudiantes encontrarán recursos como programaciones de clases, libros de calificaciones y hojas de asistencia. Organice su vida familiar con planificadores de comidas, listas y registros de ejercicio. Cada plantilla ha sido cuidadosamente diseñada, perfeccionada y mejorada a lo largo del tiempo gracias a los comentarios de miles de usuarios.</t>
   </si>
   <si>
-    <t>Documentacion</t>
-  </si>
-  <si>
-    <t>Base de datos</t>
-  </si>
-  <si>
     <t>Pau</t>
   </si>
   <si>
-    <t>Definición de requisitos funcionales y no funcionales</t>
-  </si>
-  <si>
-    <t>Diagramas de Casos de Uso</t>
-  </si>
-  <si>
-    <t>Creación del Diagrama Entidad-Relación (E-R)</t>
-  </si>
-  <si>
-    <t>Creación del Diagrama de Clases</t>
-  </si>
-  <si>
-    <t>Programación de funciones y triggers</t>
-  </si>
-  <si>
-    <t>Creación de usuarios y asignación de permisos</t>
-  </si>
-  <si>
     <t>Despliegue local (XAMPP/MySQL) y verificación</t>
   </si>
   <si>
@@ -249,9 +225,6 @@
     <t>Generación de datos de prueba (Scripts Inserts)</t>
   </si>
   <si>
-    <t>Servidor Java y Sockets</t>
-  </si>
-  <si>
     <t>Configuración Eclipse e Hibernate</t>
   </si>
   <si>
@@ -261,37 +234,64 @@
     <t>Bucle ServerSocket multihilo</t>
   </si>
   <si>
-    <t>Lógica respuestas cliente (Protocolo Sockets)</t>
-  </si>
-  <si>
-    <t>Aplicación Escritorio (JavaFX)</t>
-  </si>
-  <si>
-    <t>Diseño Vistas XML y Controladores</t>
-  </si>
-  <si>
     <t>Conexión Socket Cliente al Servidor</t>
   </si>
   <si>
-    <t>Gestión CRUD de Pacientes y generación QR</t>
-  </si>
-  <si>
-    <t>Aplicación Móvil (Android)</t>
-  </si>
-  <si>
-    <t>Diseño Interfaz UI en Kotlin</t>
-  </si>
-  <si>
     <t>Conexión Socket en hilo secundario (Coroutines)</t>
   </si>
   <si>
-    <t>Integración lectura QR con cámara</t>
-  </si>
-  <si>
-    <t>Tarea 5: Bibliografía Manual de instalación y Manual de usuario</t>
-  </si>
-  <si>
-    <t>Tarea 6:Preparacion video y entrega</t>
+    <t>Documentación y Diseño</t>
+  </si>
+  <si>
+    <t>Tarea 3.1: Definición de requisitos funcionales y no funcionales</t>
+  </si>
+  <si>
+    <t>Tarea 3.2: Diagramas de Casos de Uso</t>
+  </si>
+  <si>
+    <t>Tarea 3.3: Creación del Diagrama Entidad-Relación (E-R)</t>
+  </si>
+  <si>
+    <t>Tarea 3.4: Creación del Diagrama de Clases y Wireframes</t>
+  </si>
+  <si>
+    <t>Tarea 5: Bibliografía, Manual de instalación y Manual de usuario</t>
+  </si>
+  <si>
+    <t>Tarea 6: Preparación del vídeo y entrega final</t>
+  </si>
+  <si>
+    <t>Base de Datos</t>
+  </si>
+  <si>
+    <t>Restricciones de unicidad (citas) e integridad referencial</t>
+  </si>
+  <si>
+    <t>Creación de usuarios y asignación de permisos mínimos</t>
+  </si>
+  <si>
+    <t>Servidor Java, Seguridad y Pruebas Unitarias</t>
+  </si>
+  <si>
+    <t>Protocolo Sockets, seguridad Hash/Roles y pruebas JUnit</t>
+  </si>
+  <si>
+    <t>Aplicación Escritorio (Java Swing)</t>
+  </si>
+  <si>
+    <t>Diseño de ventanas en Java Swing (JFrame/JPanel)</t>
+  </si>
+  <si>
+    <t>Módulos de Pacientes, Agenda de Citas e Historial Clínico</t>
+  </si>
+  <si>
+    <t>Aplicación Móvil Android y Pruebas de Integración</t>
+  </si>
+  <si>
+    <t>Diseño de layouts XML e interfaz en Kotlin</t>
+  </si>
+  <si>
+    <t>Vistas de Ficha Rápida, Observaciones y Pruebas de Integración</t>
   </si>
 </sst>
 </file>
@@ -1384,6 +1384,12 @@
     <xf numFmtId="168" fontId="9" fillId="46" borderId="2" xfId="10" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
     <xf numFmtId="167" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1395,12 +1401,6 @@
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2011,48 +2011,48 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:CG41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="42" customWidth="1"/>
-    <col min="2" max="2" width="64.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="5" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="2.7109375" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" hidden="1" customWidth="1"/>
-    <col min="9" max="14" width="3.28515625" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" customWidth="1"/>
-    <col min="16" max="49" width="3.28515625" customWidth="1"/>
-    <col min="50" max="50" width="7.140625" customWidth="1"/>
-    <col min="51" max="56" width="3.28515625" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="42" customWidth="1"/>
+    <col min="2" max="2" width="64.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" hidden="1" customWidth="1"/>
+    <col min="9" max="14" width="3.33203125" customWidth="1"/>
+    <col min="15" max="15" width="9.6640625" customWidth="1"/>
+    <col min="16" max="49" width="3.33203125" customWidth="1"/>
+    <col min="50" max="50" width="7.109375" customWidth="1"/>
+    <col min="51" max="56" width="3.33203125" customWidth="1"/>
     <col min="57" max="57" width="7" customWidth="1"/>
-    <col min="58" max="63" width="3.28515625" customWidth="1"/>
-    <col min="64" max="64" width="6.140625" customWidth="1"/>
-    <col min="65" max="65" width="2.7109375" customWidth="1"/>
-    <col min="66" max="66" width="3.5703125" customWidth="1"/>
-    <col min="67" max="67" width="2.42578125" customWidth="1"/>
-    <col min="68" max="68" width="4.28515625" customWidth="1"/>
-    <col min="69" max="69" width="3.5703125" customWidth="1"/>
-    <col min="70" max="70" width="2.85546875" customWidth="1"/>
-    <col min="71" max="71" width="8.140625" customWidth="1"/>
-    <col min="72" max="72" width="2.7109375" customWidth="1"/>
-    <col min="73" max="73" width="3.5703125" customWidth="1"/>
-    <col min="74" max="74" width="2.42578125" customWidth="1"/>
-    <col min="75" max="75" width="4.28515625" customWidth="1"/>
-    <col min="76" max="76" width="3.5703125" customWidth="1"/>
-    <col min="77" max="77" width="2.85546875" customWidth="1"/>
-    <col min="78" max="78" width="8.7109375" customWidth="1"/>
-    <col min="79" max="79" width="2.7109375" customWidth="1"/>
-    <col min="80" max="80" width="3.5703125" customWidth="1"/>
-    <col min="81" max="81" width="2.42578125" customWidth="1"/>
-    <col min="82" max="82" width="4.28515625" customWidth="1"/>
-    <col min="83" max="83" width="3.5703125" customWidth="1"/>
-    <col min="84" max="84" width="2.85546875" customWidth="1"/>
-    <col min="85" max="85" width="5.28515625" customWidth="1"/>
+    <col min="58" max="63" width="3.33203125" customWidth="1"/>
+    <col min="64" max="64" width="6.109375" customWidth="1"/>
+    <col min="65" max="65" width="2.6640625" customWidth="1"/>
+    <col min="66" max="66" width="3.5546875" customWidth="1"/>
+    <col min="67" max="67" width="2.44140625" customWidth="1"/>
+    <col min="68" max="68" width="4.33203125" customWidth="1"/>
+    <col min="69" max="69" width="3.5546875" customWidth="1"/>
+    <col min="70" max="70" width="2.88671875" customWidth="1"/>
+    <col min="71" max="71" width="8.109375" customWidth="1"/>
+    <col min="72" max="72" width="2.6640625" customWidth="1"/>
+    <col min="73" max="73" width="3.5546875" customWidth="1"/>
+    <col min="74" max="74" width="2.44140625" customWidth="1"/>
+    <col min="75" max="75" width="4.33203125" customWidth="1"/>
+    <col min="76" max="76" width="3.5546875" customWidth="1"/>
+    <col min="77" max="77" width="2.88671875" customWidth="1"/>
+    <col min="78" max="78" width="8.6640625" customWidth="1"/>
+    <col min="79" max="79" width="2.6640625" customWidth="1"/>
+    <col min="80" max="80" width="3.5546875" customWidth="1"/>
+    <col min="81" max="81" width="2.44140625" customWidth="1"/>
+    <col min="82" max="82" width="4.33203125" customWidth="1"/>
+    <col min="83" max="83" width="3.5546875" customWidth="1"/>
+    <col min="84" max="84" width="2.88671875" customWidth="1"/>
+    <col min="85" max="85" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
@@ -2079,145 +2079,145 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="42" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="100" t="s">
+      <c r="C3" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="101"/>
-      <c r="E3" s="99">
+      <c r="D3" s="97"/>
+      <c r="E3" s="101">
         <v>46293</v>
       </c>
-      <c r="F3" s="99"/>
+      <c r="F3" s="101"/>
     </row>
-    <row r="4" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:85" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="101"/>
+      <c r="D4" s="97"/>
       <c r="E4" s="7">
         <v>1</v>
       </c>
-      <c r="I4" s="96">
+      <c r="I4" s="98">
         <f>I5</f>
         <v>46293</v>
       </c>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
-      <c r="L4" s="97"/>
-      <c r="M4" s="97"/>
-      <c r="N4" s="97"/>
-      <c r="O4" s="98"/>
-      <c r="P4" s="96">
+      <c r="J4" s="99"/>
+      <c r="K4" s="99"/>
+      <c r="L4" s="99"/>
+      <c r="M4" s="99"/>
+      <c r="N4" s="99"/>
+      <c r="O4" s="100"/>
+      <c r="P4" s="98">
         <f>P5</f>
         <v>46300</v>
       </c>
-      <c r="Q4" s="97"/>
-      <c r="R4" s="97"/>
-      <c r="S4" s="97"/>
-      <c r="T4" s="97"/>
-      <c r="U4" s="97"/>
-      <c r="V4" s="98"/>
-      <c r="W4" s="96">
+      <c r="Q4" s="99"/>
+      <c r="R4" s="99"/>
+      <c r="S4" s="99"/>
+      <c r="T4" s="99"/>
+      <c r="U4" s="99"/>
+      <c r="V4" s="100"/>
+      <c r="W4" s="98">
         <f>W5</f>
         <v>46307</v>
       </c>
-      <c r="X4" s="97"/>
-      <c r="Y4" s="97"/>
-      <c r="Z4" s="97"/>
-      <c r="AA4" s="97"/>
-      <c r="AB4" s="97"/>
-      <c r="AC4" s="98"/>
-      <c r="AD4" s="96">
+      <c r="X4" s="99"/>
+      <c r="Y4" s="99"/>
+      <c r="Z4" s="99"/>
+      <c r="AA4" s="99"/>
+      <c r="AB4" s="99"/>
+      <c r="AC4" s="100"/>
+      <c r="AD4" s="98">
         <f>AD5</f>
         <v>46314</v>
       </c>
-      <c r="AE4" s="97"/>
-      <c r="AF4" s="97"/>
-      <c r="AG4" s="97"/>
-      <c r="AH4" s="97"/>
-      <c r="AI4" s="97"/>
-      <c r="AJ4" s="98"/>
-      <c r="AK4" s="96">
+      <c r="AE4" s="99"/>
+      <c r="AF4" s="99"/>
+      <c r="AG4" s="99"/>
+      <c r="AH4" s="99"/>
+      <c r="AI4" s="99"/>
+      <c r="AJ4" s="100"/>
+      <c r="AK4" s="98">
         <f>AK5</f>
         <v>46321</v>
       </c>
-      <c r="AL4" s="97"/>
-      <c r="AM4" s="97"/>
-      <c r="AN4" s="97"/>
-      <c r="AO4" s="97"/>
-      <c r="AP4" s="97"/>
-      <c r="AQ4" s="98"/>
-      <c r="AR4" s="96">
+      <c r="AL4" s="99"/>
+      <c r="AM4" s="99"/>
+      <c r="AN4" s="99"/>
+      <c r="AO4" s="99"/>
+      <c r="AP4" s="99"/>
+      <c r="AQ4" s="100"/>
+      <c r="AR4" s="98">
         <f>AR5</f>
         <v>46328</v>
       </c>
-      <c r="AS4" s="97"/>
-      <c r="AT4" s="97"/>
-      <c r="AU4" s="97"/>
-      <c r="AV4" s="97"/>
-      <c r="AW4" s="97"/>
-      <c r="AX4" s="98"/>
-      <c r="AY4" s="96">
+      <c r="AS4" s="99"/>
+      <c r="AT4" s="99"/>
+      <c r="AU4" s="99"/>
+      <c r="AV4" s="99"/>
+      <c r="AW4" s="99"/>
+      <c r="AX4" s="100"/>
+      <c r="AY4" s="98">
         <f>AY5</f>
         <v>46335</v>
       </c>
-      <c r="AZ4" s="97"/>
-      <c r="BA4" s="97"/>
-      <c r="BB4" s="97"/>
-      <c r="BC4" s="97"/>
-      <c r="BD4" s="97"/>
-      <c r="BE4" s="98"/>
-      <c r="BF4" s="96">
+      <c r="AZ4" s="99"/>
+      <c r="BA4" s="99"/>
+      <c r="BB4" s="99"/>
+      <c r="BC4" s="99"/>
+      <c r="BD4" s="99"/>
+      <c r="BE4" s="100"/>
+      <c r="BF4" s="98">
         <f>BF5</f>
         <v>46342</v>
       </c>
-      <c r="BG4" s="97"/>
-      <c r="BH4" s="97"/>
-      <c r="BI4" s="97"/>
-      <c r="BJ4" s="97"/>
-      <c r="BK4" s="97"/>
-      <c r="BL4" s="98"/>
-      <c r="BM4" s="96">
+      <c r="BG4" s="99"/>
+      <c r="BH4" s="99"/>
+      <c r="BI4" s="99"/>
+      <c r="BJ4" s="99"/>
+      <c r="BK4" s="99"/>
+      <c r="BL4" s="100"/>
+      <c r="BM4" s="98">
         <f>BM5</f>
         <v>46349</v>
       </c>
-      <c r="BN4" s="97"/>
-      <c r="BO4" s="97"/>
-      <c r="BP4" s="97"/>
-      <c r="BQ4" s="97"/>
-      <c r="BR4" s="97"/>
-      <c r="BS4" s="98"/>
-      <c r="BT4" s="96">
+      <c r="BN4" s="99"/>
+      <c r="BO4" s="99"/>
+      <c r="BP4" s="99"/>
+      <c r="BQ4" s="99"/>
+      <c r="BR4" s="99"/>
+      <c r="BS4" s="100"/>
+      <c r="BT4" s="98">
         <f>BT5</f>
         <v>46356</v>
       </c>
-      <c r="BU4" s="97"/>
-      <c r="BV4" s="97"/>
-      <c r="BW4" s="97"/>
-      <c r="BX4" s="97"/>
-      <c r="BY4" s="97"/>
-      <c r="BZ4" s="98"/>
-      <c r="CA4" s="96">
+      <c r="BU4" s="99"/>
+      <c r="BV4" s="99"/>
+      <c r="BW4" s="99"/>
+      <c r="BX4" s="99"/>
+      <c r="BY4" s="99"/>
+      <c r="BZ4" s="100"/>
+      <c r="CA4" s="98">
         <f>CA5</f>
         <v>46363</v>
       </c>
-      <c r="CB4" s="97"/>
-      <c r="CC4" s="97"/>
-      <c r="CD4" s="97"/>
-      <c r="CE4" s="97"/>
-      <c r="CF4" s="97"/>
-      <c r="CG4" s="98"/>
+      <c r="CB4" s="99"/>
+      <c r="CC4" s="99"/>
+      <c r="CD4" s="99"/>
+      <c r="CE4" s="99"/>
+      <c r="CF4" s="99"/>
+      <c r="CG4" s="100"/>
     </row>
-    <row r="5" spans="1:85" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:85" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="43" t="s">
         <v>4</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>46369</v>
       </c>
     </row>
-    <row r="6" spans="1:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="43" t="s">
         <v>5</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>d</v>
       </c>
     </row>
-    <row r="7" spans="1:85" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:85" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="42" t="s">
         <v>6</v>
       </c>
@@ -2956,12 +2956,12 @@
       <c r="CF7" s="28"/>
       <c r="CG7" s="28"/>
     </row>
-    <row r="8" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="43" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C8" s="49"/>
       <c r="D8" s="16"/>
@@ -2969,12 +2969,12 @@
         <v>46293</v>
       </c>
       <c r="F8" s="65">
-        <v>46364</v>
+        <v>46367</v>
       </c>
       <c r="G8" s="14"/>
       <c r="H8" s="14">
         <f t="shared" ref="H8:H38" si="23">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I8" s="28"/>
       <c r="J8" s="28"/>
@@ -3054,15 +3054,15 @@
       <c r="CF8" s="28"/>
       <c r="CG8" s="28"/>
     </row>
-    <row r="9" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="43" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D9" s="17">
         <v>0</v>
@@ -3071,12 +3071,12 @@
         <v>46293</v>
       </c>
       <c r="F9" s="75">
-        <v>46299</v>
+        <v>46297</v>
       </c>
       <c r="G9" s="14"/>
       <c r="H9" s="14">
         <f t="shared" si="23"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I9" s="28"/>
       <c r="J9" s="28"/>
@@ -3156,15 +3156,15 @@
       <c r="CF9" s="28"/>
       <c r="CG9" s="28"/>
     </row>
-    <row r="10" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="43" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" s="17">
         <v>0</v>
@@ -3173,12 +3173,12 @@
         <v>46300</v>
       </c>
       <c r="F10" s="75">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="G10" s="14"/>
       <c r="H10" s="14">
         <f t="shared" si="23"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I10" s="28"/>
       <c r="J10" s="28"/>
@@ -3258,13 +3258,13 @@
       <c r="CF10" s="28"/>
       <c r="CG10" s="28"/>
     </row>
-    <row r="11" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="42"/>
       <c r="B11" s="56" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D11" s="17">
         <v>0</v>
@@ -3355,13 +3355,13 @@
       <c r="CF11" s="28"/>
       <c r="CG11" s="28"/>
     </row>
-    <row r="12" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="42"/>
       <c r="B12" s="56" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D12" s="17">
         <v>0</v>
@@ -3452,13 +3452,13 @@
       <c r="CF12" s="28"/>
       <c r="CG12" s="28"/>
     </row>
-    <row r="13" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="42"/>
       <c r="B13" s="56" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D13" s="17">
         <v>0</v>
@@ -3467,7 +3467,7 @@
         <v>46311</v>
       </c>
       <c r="F13" s="75">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
@@ -3549,19 +3549,19 @@
       <c r="CF13" s="28"/>
       <c r="CG13" s="28"/>
     </row>
-    <row r="14" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="42"/>
       <c r="B14" s="56" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C14" s="50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" s="17">
         <v>0</v>
       </c>
       <c r="E14" s="75">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" s="75">
         <v>46316</v>
@@ -3646,22 +3646,22 @@
       <c r="CF14" s="28"/>
       <c r="CG14" s="28"/>
     </row>
-    <row r="15" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="42"/>
       <c r="B15" s="56" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C15" s="50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" s="17">
         <v>0</v>
       </c>
       <c r="E15" s="75">
-        <v>46358</v>
+        <v>46359</v>
       </c>
       <c r="F15" s="75">
-        <v>46359</v>
+        <v>46360</v>
       </c>
       <c r="G15" s="14"/>
       <c r="H15" s="14">
@@ -3746,19 +3746,19 @@
       <c r="CF15" s="28"/>
       <c r="CG15" s="28"/>
     </row>
-    <row r="16" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="42"/>
       <c r="B16" s="56" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D16" s="17">
         <v>0</v>
       </c>
       <c r="E16" s="75">
-        <v>46362</v>
+        <v>46363</v>
       </c>
       <c r="F16" s="75">
         <v>46364</v>
@@ -3843,19 +3843,19 @@
       <c r="CF16" s="28"/>
       <c r="CG16" s="28"/>
     </row>
-    <row r="17" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="42"/>
       <c r="B17" s="56" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C17" s="50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D17" s="17">
         <v>0</v>
       </c>
       <c r="E17" s="75">
-        <v>46364</v>
+        <v>46365</v>
       </c>
       <c r="F17" s="75">
         <v>46367</v>
@@ -3863,7 +3863,7 @@
       <c r="G17" s="14"/>
       <c r="H17" s="14">
         <f t="shared" si="23"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I17" s="28"/>
       <c r="J17" s="28"/>
@@ -3943,12 +3943,12 @@
       <c r="CF17" s="28"/>
       <c r="CG17" s="28"/>
     </row>
-    <row r="18" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="43" t="s">
         <v>10</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C18" s="51"/>
       <c r="D18" s="19"/>
@@ -3956,12 +3956,12 @@
         <v>46317</v>
       </c>
       <c r="F18" s="67">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="G18" s="14"/>
       <c r="H18" s="14">
         <f t="shared" si="23"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I18" s="28"/>
       <c r="J18" s="28"/>
@@ -4041,13 +4041,13 @@
       <c r="CF18" s="28"/>
       <c r="CG18" s="28"/>
     </row>
-    <row r="19" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="43"/>
       <c r="B19" s="57" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C19" s="52" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D19" s="20">
         <v>0</v>
@@ -4056,12 +4056,12 @@
         <v>46317</v>
       </c>
       <c r="F19" s="76">
-        <v>46319</v>
+        <v>46318</v>
       </c>
       <c r="G19" s="14"/>
       <c r="H19" s="14">
         <f t="shared" si="23"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19" s="28"/>
       <c r="J19" s="28"/>
@@ -4141,19 +4141,19 @@
       <c r="CF19" s="28"/>
       <c r="CG19" s="28"/>
     </row>
-    <row r="20" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="42"/>
       <c r="B20" s="57" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C20" s="52" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D20" s="20">
         <v>0</v>
       </c>
       <c r="E20" s="76">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" s="76">
         <v>46322</v>
@@ -4161,7 +4161,7 @@
       <c r="G20" s="14"/>
       <c r="H20" s="14">
         <f t="shared" si="23"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I20" s="28"/>
       <c r="J20" s="28"/>
@@ -4241,13 +4241,13 @@
       <c r="CF20" s="28"/>
       <c r="CG20" s="28"/>
     </row>
-    <row r="21" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="42"/>
       <c r="B21" s="57" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C21" s="52" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D21" s="20">
         <v>0</v>
@@ -4341,13 +4341,13 @@
       <c r="CF21" s="28"/>
       <c r="CG21" s="28"/>
     </row>
-    <row r="22" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="42"/>
       <c r="B22" s="57" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C22" s="52" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D22" s="20">
         <v>0</v>
@@ -4356,12 +4356,12 @@
         <v>46324</v>
       </c>
       <c r="F22" s="76">
-        <v>46325</v>
+        <v>46324</v>
       </c>
       <c r="G22" s="14"/>
       <c r="H22" s="14">
         <f t="shared" si="23"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" s="28"/>
       <c r="J22" s="28"/>
@@ -4441,22 +4441,22 @@
       <c r="CF22" s="28"/>
       <c r="CG22" s="28"/>
     </row>
-    <row r="23" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="42"/>
       <c r="B23" s="57" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D23" s="20">
         <v>0</v>
       </c>
       <c r="E23" s="76">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="F23" s="76">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="G23" s="14"/>
       <c r="H23" s="14">
@@ -4541,25 +4541,25 @@
       <c r="CF23" s="28"/>
       <c r="CG23" s="28"/>
     </row>
-    <row r="24" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="42" t="s">
         <v>11</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C24" s="53"/>
       <c r="D24" s="22"/>
       <c r="E24" s="68">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F24" s="69">
-        <v>46340</v>
+        <v>46339</v>
       </c>
       <c r="G24" s="14"/>
       <c r="H24" s="14">
         <f t="shared" si="23"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I24" s="28"/>
       <c r="J24" s="28"/>
@@ -4639,19 +4639,19 @@
       <c r="CF24" s="28"/>
       <c r="CG24" s="28"/>
     </row>
-    <row r="25" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="42"/>
       <c r="B25" s="58" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C25" s="54" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D25" s="23">
         <v>0</v>
       </c>
       <c r="E25" s="77">
-        <v>46327</v>
+        <v>46328</v>
       </c>
       <c r="F25" s="77">
         <v>46329</v>
@@ -4659,7 +4659,7 @@
       <c r="G25" s="14"/>
       <c r="H25" s="14">
         <f t="shared" si="23"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25" s="28"/>
       <c r="J25" s="28"/>
@@ -4739,13 +4739,13 @@
       <c r="CF25" s="28"/>
       <c r="CG25" s="28"/>
     </row>
-    <row r="26" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="42"/>
       <c r="B26" s="58" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C26" s="54" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D26" s="23">
         <v>0</v>
@@ -4839,19 +4839,19 @@
       <c r="CF26" s="28"/>
       <c r="CG26" s="28"/>
     </row>
-    <row r="27" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="42"/>
       <c r="B27" s="58" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C27" s="54" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D27" s="23">
         <v>0</v>
       </c>
       <c r="E27" s="77">
-        <v>46333</v>
+        <v>46335</v>
       </c>
       <c r="F27" s="77">
         <v>46336</v>
@@ -4859,7 +4859,7 @@
       <c r="G27" s="14"/>
       <c r="H27" s="14">
         <f t="shared" si="23"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I27" s="28"/>
       <c r="J27" s="28"/>
@@ -4939,13 +4939,13 @@
       <c r="CF27" s="28"/>
       <c r="CG27" s="28"/>
     </row>
-    <row r="28" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="42"/>
       <c r="B28" s="58" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C28" s="54" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D28" s="23">
         <v>0</v>
@@ -4954,12 +4954,12 @@
         <v>46337</v>
       </c>
       <c r="F28" s="77">
-        <v>46340</v>
+        <v>46339</v>
       </c>
       <c r="G28" s="14"/>
       <c r="H28" s="14">
         <f t="shared" si="23"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I28" s="28"/>
       <c r="J28" s="28"/>
@@ -5039,20 +5039,20 @@
       <c r="CF28" s="28"/>
       <c r="CG28" s="28"/>
     </row>
-    <row r="29" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="42" t="s">
         <v>12</v>
       </c>
       <c r="B29" s="81" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C29" s="79"/>
       <c r="D29" s="80"/>
       <c r="E29" s="82">
-        <v>46341</v>
+        <v>46342</v>
       </c>
       <c r="F29" s="83">
-        <v>46349</v>
+        <v>46350</v>
       </c>
       <c r="G29" s="14"/>
       <c r="H29" s="14">
@@ -5137,21 +5137,21 @@
       <c r="CF29" s="28"/>
       <c r="CG29" s="28"/>
     </row>
-    <row r="30" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:85" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="43" t="s">
         <v>13</v>
       </c>
       <c r="B30" s="84" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C30" s="85" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D30" s="86">
         <v>0</v>
       </c>
       <c r="E30" s="87">
-        <v>46341</v>
+        <v>46342</v>
       </c>
       <c r="F30" s="87">
         <v>46344</v>
@@ -5159,7 +5159,7 @@
       <c r="G30" s="14"/>
       <c r="H30" s="14">
         <f t="shared" si="23"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I30" s="28"/>
       <c r="J30" s="28"/>
@@ -5239,12 +5239,12 @@
       <c r="CF30" s="28"/>
       <c r="CG30" s="28"/>
     </row>
-    <row r="31" spans="1:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="84" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C31" s="85" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D31" s="86">
         <v>0</v>
@@ -5338,26 +5338,26 @@
       <c r="CF31" s="28"/>
       <c r="CG31" s="28"/>
     </row>
-    <row r="32" spans="1:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="84" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C32" s="85" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D32" s="86">
         <v>0</v>
       </c>
       <c r="E32" s="87">
-        <v>46347</v>
+        <v>46349</v>
       </c>
       <c r="F32" s="87">
-        <v>46349</v>
+        <v>46350</v>
       </c>
       <c r="G32" s="14"/>
       <c r="H32" s="14">
         <f t="shared" si="23"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
@@ -5437,17 +5437,17 @@
       <c r="CF32" s="28"/>
       <c r="CG32" s="28"/>
     </row>
-    <row r="33" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B33" s="92" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C33" s="93"/>
       <c r="D33" s="94"/>
       <c r="E33" s="95">
-        <v>46350</v>
+        <v>46351</v>
       </c>
       <c r="F33" s="95">
-        <v>46357</v>
+        <v>46360</v>
       </c>
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
@@ -5529,21 +5529,21 @@
       <c r="CF33" s="28"/>
       <c r="CG33" s="28"/>
     </row>
-    <row r="34" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="88" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C34" s="89" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D34" s="90">
         <v>0</v>
       </c>
       <c r="E34" s="91">
-        <v>46350</v>
+        <v>46351</v>
       </c>
       <c r="F34" s="91">
-        <v>46352</v>
+        <v>46353</v>
       </c>
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
@@ -5625,21 +5625,21 @@
       <c r="CF34" s="28"/>
       <c r="CG34" s="28"/>
     </row>
-    <row r="35" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="88" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C35" s="89" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D35" s="90">
         <v>0</v>
       </c>
       <c r="E35" s="91">
-        <v>46353</v>
+        <v>46356</v>
       </c>
       <c r="F35" s="91">
-        <v>46355</v>
+        <v>46357</v>
       </c>
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
@@ -5721,26 +5721,26 @@
       <c r="CF35" s="28"/>
       <c r="CG35" s="28"/>
     </row>
-    <row r="36" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="88" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C36" s="89" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D36" s="90">
         <v>0</v>
       </c>
       <c r="E36" s="91">
-        <v>46356</v>
+        <v>46358</v>
       </c>
       <c r="F36" s="91">
-        <v>46357</v>
+        <v>46360</v>
       </c>
       <c r="G36" s="14"/>
       <c r="H36" s="14">
         <f t="shared" si="23"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" s="28"/>
       <c r="J36" s="28"/>
@@ -5820,7 +5820,7 @@
       <c r="CF36" s="28"/>
       <c r="CG36" s="28"/>
     </row>
-    <row r="37" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="59"/>
       <c r="C37" s="55"/>
       <c r="D37" s="13"/>
@@ -5909,7 +5909,7 @@
       <c r="CF37" s="28"/>
       <c r="CG37" s="28"/>
     </row>
-    <row r="38" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:85" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="24" t="s">
         <v>18</v>
       </c>
@@ -6000,23 +6000,18 @@
       <c r="CF38" s="30"/>
       <c r="CG38" s="30"/>
     </row>
-    <row r="39" spans="2:85" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:85" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G39" s="6"/>
     </row>
-    <row r="40" spans="2:85" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:85" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="11"/>
       <c r="F40" s="44"/>
     </row>
-    <row r="41" spans="2:85" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:85" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C41" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
     <mergeCell ref="BM4:BS4"/>
     <mergeCell ref="BT4:BZ4"/>
     <mergeCell ref="CA4:CG4"/>
@@ -6026,6 +6021,11 @@
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
   </mergeCells>
   <conditionalFormatting sqref="D7:D38">
     <cfRule type="dataBar" priority="23">
@@ -6065,7 +6065,7 @@
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="48" fitToHeight="0" orientation="landscape" r:id="rId3"/>
+  <pageSetup paperSize="9" scale="32" fitToHeight="0" orientation="landscape" r:id="rId3"/>
   <headerFooter differentFirst="1" scaleWithDoc="0">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -6096,86 +6096,86 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="87.140625" style="32" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="87.109375" style="32" customWidth="1"/>
+    <col min="2" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="1:2" s="34" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="46.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:2" s="34" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="33"/>
     </row>
-    <row r="3" spans="1:2" s="38" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="38" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="63" t="s">
         <v>27</v>
       </c>
       <c r="B3" s="39"/>
     </row>
-    <row r="4" spans="1:2" s="35" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2" s="35" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A4" s="36" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="74.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="37" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="36" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:2" s="32" customFormat="1" ht="215.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" s="32" customFormat="1" ht="215.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="41" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:2" s="35" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:2" s="35" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A8" s="36" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="37" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:2" s="32" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" s="32" customFormat="1" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="40" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="35" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:2" s="35" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A11" s="36" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:2" s="32" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" s="32" customFormat="1" ht="27.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="40" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:2" s="35" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:2" s="35" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A14" s="36" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="96.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" ht="96.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="37" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="90" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A16" s="37" t="s">
         <v>40</v>
       </c>
@@ -6194,35 +6194,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6510,27 +6481,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6549,4 +6529,31 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="16c05727-aa75-4e4a-9b5f-8a80a1165891"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>